--- a/erp-server/erp-server-file/src/main/resources/excel/wms/sampleAdjustmentInfoExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/sampleAdjustmentInfoExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24945" windowHeight="17655"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>审核完成时间</t>
   </si>
   <si>
-    <t>退回人</t>
+    <t>调整人</t>
   </si>
   <si>
     <t>创建人</t>
@@ -118,7 +118,7 @@
     <t>{.approveTime}</t>
   </si>
   <si>
-    <t>{.userName}</t>
+    <t>{.adjustmentUserName}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
